--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0004_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0004_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -756,7 +757,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.024613566998129346</v>
+        <v>0.024613566998129347</v>
       </c>
       <c r="B19" s="0">
         <v>0.087719298245613961</v>
@@ -917,7 +918,7 @@
         <v>0.29165979786707896</v>
       </c>
       <c r="D23" s="0">
-        <v>0.48325439376818174</v>
+        <v>0.48325439376818175</v>
       </c>
       <c r="E23" s="0">
         <v>1.2750977057788109</v>
@@ -941,7 +942,7 @@
         <v>0.64432989690721587</v>
       </c>
       <c r="L23" s="0">
-        <v>0.43697322178334796</v>
+        <v>0.43697322178334797</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +950,7 @@
         <v>1.1026878015161978</v>
       </c>
       <c r="B24" s="0">
-        <v>1.4035087719298271</v>
+        <v>1.4035087719298272</v>
       </c>
       <c r="C24" s="0">
         <v>0.54020466909293907</v>
@@ -1180,7 +1181,7 @@
         <v>6.3157894736842053</v>
       </c>
       <c r="C30" s="0">
-        <v>4.4294246693465515</v>
+        <v>4.4294246693465516</v>
       </c>
       <c r="D30" s="0">
         <v>5.9505205202798495</v>
@@ -1201,7 +1202,7 @@
         <v>4.6652499453834038</v>
       </c>
       <c r="J30" s="0">
-        <v>5.1527419948472541</v>
+        <v>5.1527419948472542</v>
       </c>
       <c r="K30" s="0">
         <v>10.438144329896899</v>
@@ -1221,13 +1222,13 @@
         <v>4.5739864822024083</v>
       </c>
       <c r="D31" s="0">
-        <v>5.4336066164979639</v>
+        <v>5.433606616497964</v>
       </c>
       <c r="E31" s="0">
         <v>3.637936692622092</v>
       </c>
       <c r="F31" s="0">
-        <v>4.3645162464068656</v>
+        <v>4.3645162464068657</v>
       </c>
       <c r="G31" s="0">
         <v>4.6268356467511529</v>
@@ -1303,10 +1304,10 @@
         <v>3.4953310062949337</v>
       </c>
       <c r="F33" s="0">
-        <v>3.8878579485500095</v>
+        <v>3.8878579485500096</v>
       </c>
       <c r="G33" s="0">
-        <v>3.6813518406759171</v>
+        <v>3.6813518406759172</v>
       </c>
       <c r="H33" s="0">
         <v>3.6187013577231122</v>
@@ -1350,7 +1351,7 @@
         <v>2.8404249275691615</v>
       </c>
       <c r="I34" s="0">
-        <v>4.4964350261166572</v>
+        <v>4.4964350261166573</v>
       </c>
       <c r="J34" s="0">
         <v>3.2572690467427279</v>
@@ -1359,7 +1360,7 @@
         <v>3.0927835051546366</v>
       </c>
       <c r="L34" s="0">
-        <v>3.7197151121201721</v>
+        <v>3.7197151121201722</v>
       </c>
     </row>
     <row r="35">
@@ -1417,7 +1418,7 @@
         <v>3.1104746561651573</v>
       </c>
       <c r="F36" s="0">
-        <v>3.3802714405268683</v>
+        <v>3.3802714405268684</v>
       </c>
       <c r="G36" s="0">
         <v>2.6352846509756565</v>
@@ -1502,7 +1503,7 @@
         <v>2.8404249275691615</v>
       </c>
       <c r="I38" s="0">
-        <v>3.3683541538400394</v>
+        <v>3.3683541538400395</v>
       </c>
       <c r="J38" s="0">
         <v>2.2819285977180694</v>
@@ -1554,7 +1555,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>2.7665649305897388</v>
+        <v>2.7665649305897389</v>
       </c>
       <c r="B40" s="0">
         <v>0.87719298245613953</v>
@@ -1630,7 +1631,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>2.7665649305897388</v>
+        <v>2.7665649305897389</v>
       </c>
       <c r="B42" s="0">
         <v>0.35087719298245584</v>
@@ -1785,7 +1786,7 @@
         <v>2.2447573102293963</v>
       </c>
       <c r="B46" s="0">
-        <v>2.1052631578947349</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C46" s="0">
         <v>2.1417973852065058</v>
@@ -1847,7 +1848,7 @@
         <v>2.0476256678119698</v>
       </c>
       <c r="J47" s="0">
-        <v>1.6010305483989768</v>
+        <v>1.6010305483989769</v>
       </c>
       <c r="K47" s="0">
         <v>0</v>
@@ -1917,7 +1918,7 @@
         <v>1.9312009656004812</v>
       </c>
       <c r="H49" s="0">
-        <v>1.9882974492984133</v>
+        <v>1.9882974492984134</v>
       </c>
       <c r="I49" s="0">
         <v>1.864908343429126</v>
@@ -1934,7 +1935,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.956778576351283</v>
+        <v>1.9567785763512831</v>
       </c>
       <c r="B50" s="0">
         <v>1.9298245614035072</v>
@@ -1981,7 +1982,7 @@
         <v>1.6573885035316183</v>
       </c>
       <c r="D51" s="0">
-        <v>1.5892097227898911</v>
+        <v>1.5892097227898912</v>
       </c>
       <c r="E51" s="0">
         <v>1.7351352963990556</v>
@@ -2110,7 +2111,7 @@
         <v>1.3861273646537509</v>
       </c>
       <c r="I54" s="0">
-        <v>1.1916347242358631</v>
+        <v>1.1916347242358632</v>
       </c>
       <c r="J54" s="0">
         <v>1.8586676481413307</v>
@@ -2119,7 +2120,7 @@
         <v>0.64432989690721587</v>
       </c>
       <c r="L54" s="0">
-        <v>1.4026684912760849</v>
+        <v>1.402668491276085</v>
       </c>
     </row>
     <row r="55">
@@ -2157,7 +2158,7 @@
         <v>0.5154639175257727</v>
       </c>
       <c r="L55" s="0">
-        <v>1.2627126551177172</v>
+        <v>1.2627126551177173</v>
       </c>
     </row>
     <row r="56">
@@ -2478,7 +2479,7 @@
         <v>0.29812708869280863</v>
       </c>
       <c r="E64" s="0">
-        <v>0.58295295205704178</v>
+        <v>0.58295295205704179</v>
       </c>
       <c r="F64" s="0">
         <v>0.79685623840192055</v>
@@ -2525,7 +2526,7 @@
         <v>0.74431703882518541</v>
       </c>
       <c r="H65" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.67602113276146048</v>
       </c>
       <c r="I65" s="0">
         <v>0.583901014875573</v>
@@ -2601,7 +2602,7 @@
         <v>0.78455039227519552</v>
       </c>
       <c r="H67" s="0">
-        <v>0.70442538203715221</v>
+        <v>0.70442538203715222</v>
       </c>
       <c r="I67" s="0">
         <v>0.47466783182061878</v>
@@ -2636,10 +2637,10 @@
         <v>0.62038350980606138</v>
       </c>
       <c r="G68" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H68" s="0">
-        <v>0.71010623189229038</v>
+        <v>0.71010623189229039</v>
       </c>
       <c r="I68" s="0">
         <v>0.47665388969434525</v>
@@ -2756,7 +2757,7 @@
         <v>0.54536158609327912</v>
       </c>
       <c r="I71" s="0">
-        <v>0.35351830152330604</v>
+        <v>0.35351830152330605</v>
       </c>
       <c r="J71" s="0">
         <v>0.57048214942951736</v>
@@ -2841,7 +2842,7 @@
         <v>0.25773195876288635</v>
       </c>
       <c r="L73" s="0">
-        <v>0.40120673032065401</v>
+        <v>0.40120673032065402</v>
       </c>
     </row>
     <row r="74">
@@ -2861,7 +2862,7 @@
         <v>0.17482621796592962</v>
       </c>
       <c r="F74" s="0">
-        <v>0.41116326456354801</v>
+        <v>0.41116326456354802</v>
       </c>
       <c r="G74" s="0">
         <v>0.22128344397505512</v>
@@ -2908,7 +2909,7 @@
         <v>0.35789354087371439</v>
       </c>
       <c r="I75" s="0">
-        <v>0.23435482909971977</v>
+        <v>0.23435482909971978</v>
       </c>
       <c r="J75" s="0">
         <v>0.34965034965034936</v>
@@ -2940,7 +2941,7 @@
         <v>0.32201724702543366</v>
       </c>
       <c r="G76" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H76" s="0">
         <v>0.26699994319150122</v>
@@ -3013,7 +3014,7 @@
         <v>0.084131388167904692</v>
       </c>
       <c r="F78" s="0">
-        <v>0.21649747116399209</v>
+        <v>0.2164974711639921</v>
       </c>
       <c r="G78" s="0">
         <v>0.26151679742506517</v>
@@ -3048,7 +3049,7 @@
         <v>0.067319020027408402</v>
       </c>
       <c r="E79" s="0">
-        <v>0.061457680718398459</v>
+        <v>0.06145768071839846</v>
       </c>
       <c r="F79" s="0">
         <v>0.18738856747807719</v>
@@ -3118,7 +3119,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="C81" s="0">
-        <v>0.03931066840817151</v>
+        <v>0.039310668408171511</v>
       </c>
       <c r="D81" s="0">
         <v>0.057702017166350053</v>
@@ -3156,10 +3157,10 @@
         <v>0.17543859649122986</v>
       </c>
       <c r="C82" s="0">
-        <v>0.032970238019757118</v>
+        <v>0.032970238019757119</v>
       </c>
       <c r="D82" s="0">
-        <v>0.057702017166350691</v>
+        <v>0.057702017166350692</v>
       </c>
       <c r="E82" s="0">
         <v>0.026850443032310305</v>
@@ -3209,7 +3210,7 @@
         <v>0.060350030175015036</v>
       </c>
       <c r="H83" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I83" s="0">
         <v>0.045679331095708091</v>
@@ -3247,7 +3248,7 @@
         <v>0.040233353450010022</v>
       </c>
       <c r="H84" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I84" s="0">
         <v>0.037735099600802333</v>
@@ -3273,7 +3274,7 @@
         <v>0.0088766025437806654</v>
       </c>
       <c r="D85" s="0">
-        <v>0.024042507152645855</v>
+        <v>0.024042507152645856</v>
       </c>
       <c r="E85" s="0">
         <v>0.0029833825591455568</v>
@@ -3285,7 +3286,7 @@
         <v>0.040233353450010022</v>
       </c>
       <c r="H85" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I85" s="0">
         <v>0.029790868105896578</v>
@@ -3297,7 +3298,7 @@
         <v>0.90206185567010222</v>
       </c>
       <c r="L85" s="0">
-        <v>0.057537399309551158</v>
+        <v>0.057537399309551159</v>
       </c>
     </row>
     <row r="86">
@@ -3361,7 +3362,7 @@
         <v>0.040233353450010022</v>
       </c>
       <c r="H87" s="0">
-        <v>0.068170198261659889</v>
+        <v>0.06817019826165989</v>
       </c>
       <c r="I87" s="0">
         <v>0.0099302893686321926</v>
@@ -3378,7 +3379,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B88" s="0">
         <v>0.087719298245613961</v>
@@ -3416,7 +3417,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B89" s="0">
         <v>0.26315789473684187</v>
@@ -3454,7 +3455,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B90" s="0">
         <v>0.087719298245613961</v>
